--- a/astro-site/public/dl/pizza-shop-business-plan/pizza-dough-food-cost-calculator.xlsx
+++ b/astro-site/public/dl/pizza-shop-business-plan/pizza-dough-food-cost-calculator.xlsx
@@ -3369,7 +3369,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Version 1.0 · October 2026 · aichef.pro/en/digital-products/pizza-shop-business-plan · info@aichef.pro</t>
+          <t>Version 2.2 · October 2026 · aichef.pro/en/digital-products/pizza-shop-business-plan · info@aichef.pro</t>
         </is>
       </c>
     </row>
